--- a/e2e/expectedData/sub_Master_Benefit_District.xlsx
+++ b/e2e/expectedData/sub_Master_Benefit_District.xlsx
@@ -131,7 +131,7 @@
     <t>$ 193.00</t>
   </si>
   <si>
-    <t>DILI, 26 AGUSTUS 2026</t>
+    <t>DILI, 09 SEPTEMBER 2026</t>
   </si>
   <si>
     <t>Human Resource</t>

--- a/e2e/expectedData/sub_Master_Benefit_District.xlsx
+++ b/e2e/expectedData/sub_Master_Benefit_District.xlsx
@@ -50,15 +50,51 @@
     <t>TOTAL</t>
   </si>
   <si>
+    <t>ADROALDINO DA SILVA NORONHA TOME</t>
+  </si>
+  <si>
+    <t>Customer Service Staff Manufahi</t>
+  </si>
+  <si>
+    <t>Baucau</t>
+  </si>
+  <si>
+    <t>$ 120.00</t>
+  </si>
+  <si>
+    <t>$ 65.00</t>
+  </si>
+  <si>
+    <t>$ 55.00</t>
+  </si>
+  <si>
+    <t>CELIA MARIA REGO DE FATIMA</t>
+  </si>
+  <si>
+    <t>Human Capital Operational Assistant Manager</t>
+  </si>
+  <si>
+    <t>Dili</t>
+  </si>
+  <si>
+    <t>$ 300.00</t>
+  </si>
+  <si>
+    <t>$ 10.00</t>
+  </si>
+  <si>
+    <t>$ 20.00</t>
+  </si>
+  <si>
+    <t>$ 30.00</t>
+  </si>
+  <si>
     <t>RIMBUN SIBURIAN</t>
   </si>
   <si>
     <t>Quality Assuance Senior Engineer</t>
   </si>
   <si>
-    <t>Dili</t>
-  </si>
-  <si>
     <t>$ 850.00</t>
   </si>
   <si>
@@ -71,42 +107,6 @@
     <t>$ 13.00</t>
   </si>
   <si>
-    <t>CELIA MARIA REGO DE FATIMA</t>
-  </si>
-  <si>
-    <t>Human Capital Operational Assistant Manager</t>
-  </si>
-  <si>
-    <t>$ 300.00</t>
-  </si>
-  <si>
-    <t>$ 10.00</t>
-  </si>
-  <si>
-    <t>$ 20.00</t>
-  </si>
-  <si>
-    <t>$ 30.00</t>
-  </si>
-  <si>
-    <t>ADROALDINO DA SILVA NORONHA TOME</t>
-  </si>
-  <si>
-    <t>Customer Service Staff Manufahi</t>
-  </si>
-  <si>
-    <t>Baucau</t>
-  </si>
-  <si>
-    <t>$ 120.00</t>
-  </si>
-  <si>
-    <t>$ 65.00</t>
-  </si>
-  <si>
-    <t>$ 55.00</t>
-  </si>
-  <si>
     <t>SYALDY KHARISMA ANANDA</t>
   </si>
   <si>
@@ -131,7 +131,7 @@
     <t>$ 193.00</t>
   </si>
   <si>
-    <t>DILI, 09 SEPTEMBER 2026</t>
+    <t>DILI, 10 SEPTEMBER 2026</t>
   </si>
   <si>
     <t>Human Resource</t>
@@ -622,7 +622,7 @@
         <v>1</v>
       </c>
       <c r="B5" s="3">
-        <v>81010</v>
+        <v>24016</v>
       </c>
       <c r="C5" s="3" t="s">
         <v>11</v>
@@ -643,7 +643,7 @@
         <v>16</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
     </row>
     <row r="6" spans="1:9">
@@ -654,13 +654,13 @@
         <v>92003</v>
       </c>
       <c r="C6" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D6" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="D6" s="3" t="s">
+      <c r="E6" s="3" t="s">
         <v>19</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>13</v>
       </c>
       <c r="F6" s="3" t="s">
         <v>20</v>
@@ -680,7 +680,7 @@
         <v>3</v>
       </c>
       <c r="B7" s="3">
-        <v>24016</v>
+        <v>81010</v>
       </c>
       <c r="C7" s="3" t="s">
         <v>24</v>
@@ -689,19 +689,19 @@
         <v>25</v>
       </c>
       <c r="E7" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="F7" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="F7" s="3" t="s">
+      <c r="G7" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="G7" s="3" t="s">
+      <c r="H7" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="H7" s="3" t="s">
+      <c r="I7" s="3" t="s">
         <v>29</v>
-      </c>
-      <c r="I7" s="3" t="s">
-        <v>27</v>
       </c>
     </row>
     <row r="8" spans="1:9">
